--- a/Employee_Reports_wi52/John Michael Angelo Mesina Clemen Q0549.xlsx
+++ b/Employee_Reports_wi52/John Michael Angelo Mesina Clemen Q0549.xlsx
@@ -569,11 +569,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>-106</v>
+        <v>-114</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -618,11 +618,11 @@
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>701</v>
+        <v>693</v>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -667,11 +667,11 @@
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>701</v>
+        <v>693</v>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -716,11 +716,11 @@
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -765,11 +765,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>-251</v>
+        <v>-259</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -814,11 +814,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>-100</v>
+        <v>-108</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -863,11 +863,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>-6</v>
+        <v>-14</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -912,11 +912,11 @@
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -940,20 +940,20 @@
       <c r="E11" s="4" t="inlineStr"/>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>01-Oct-2024</t>
+          <t>26-Aug-2026</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>01-Oct-2026</t>
+          <t>25-Aug-2028</t>
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>42</v>
+        <v>728</v>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
